--- a/NewShopEntry/Pampanikal/2080/9_Falgun 2080.xlsx
+++ b/NewShopEntry/Pampanikal/2080/9_Falgun 2080.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\shop-main\NewShopEntry\Pampanikal\2080\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA48ECA8-7ED5-4D85-B873-56B62328CD96}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ACF3B81-4BB9-443C-A98B-47C8D33A234A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9060" xr2:uid="{B3429875-737F-40AC-B95F-7B26A6BBCF55}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="29">
   <si>
     <t>Pampanikal</t>
   </si>
@@ -106,13 +106,19 @@
   </si>
   <si>
     <t xml:space="preserve">  11/17/2080</t>
+  </si>
+  <si>
+    <t>Reamaining</t>
+  </si>
+  <si>
+    <t>1/15/2081Cash</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -157,6 +163,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -172,7 +186,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -196,26 +210,51 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
       <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="16" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -225,13 +264,13 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -559,35 +598,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="31.2" x14ac:dyDescent="0.6">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
     </row>
     <row r="2" spans="1:5" ht="31.2" x14ac:dyDescent="0.6">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
     </row>
     <row r="3" spans="1:5" ht="31.2" x14ac:dyDescent="0.6">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="4" t="s">
         <v>2</v>
       </c>
     </row>
@@ -805,48 +844,59 @@
       <c r="E18" s="3"/>
     </row>
     <row r="19" spans="1:5" ht="46.2" x14ac:dyDescent="0.85">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="B19" s="10">
+      <c r="B19" s="16"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="15">
         <f>SUM(B4:B18,E4:E18)</f>
         <v>28245</v>
       </c>
-      <c r="C19" s="10"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="10"/>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="11"/>
-      <c r="B20" s="12"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="7"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
+      <c r="E19" s="16"/>
+    </row>
+    <row r="20" spans="1:5" ht="25.8" x14ac:dyDescent="0.5">
+      <c r="A20" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20" s="10"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="10">
+        <v>8220</v>
+      </c>
+      <c r="E20" s="10"/>
+    </row>
+    <row r="21" spans="1:5" ht="25.8" x14ac:dyDescent="0.5">
+      <c r="A21" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" s="9"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="10">
+        <f>D19-D20</f>
+        <v>20025</v>
+      </c>
+      <c r="E21" s="10"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="7"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="6"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
+      <c r="A22" s="11"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="D21:E21"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="D22:E22"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="B19:E19"/>
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="D20:E20"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="D19:E19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
